--- a/www/download/COUNTRY.SWE.zdW13.xlsx
+++ b/www/download/COUNTRY.SWE.zdW13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Suécia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.1209853786912</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.70421035800362</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.62718343458456</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.94723073282277</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.26104914409274</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.13075211422837</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.3114045632859</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9.70685325223753</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.06776946061647</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.33729552481548</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.44934438059463</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.36702534389249</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.75082699066162</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.51703522574423</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.60913399607839</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.129</t>
+          <t>0.141478044643975</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.096</t>
+          <t>0.123746949880494</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.043</t>
+          <t>0.319934388215686</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>0.230620333036318</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.198</t>
+          <t>0.220750197807577</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.301</t>
+          <t>0.150221711986649</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.391</t>
+          <t>0.144530209183577</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.393</t>
+          <t>0.0888875352483953</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.368</t>
+          <t>0.0484848190614646</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.337</t>
+          <t>-0.00575530577395322</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.349</t>
+          <t>-0.0302605767247662</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.423</t>
+          <t>-0.017641618354067</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.524</t>
+          <t>-0.0314297250240264</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.542</t>
+          <t>0.0183605815872827</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.425</t>
+          <t>0.164330807700162</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.848</t>
+          <t>0.534130262087749</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.819</t>
+          <t>0.501502362508258</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.768</t>
+          <t>0.750397767886262</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.836</t>
+          <t>0.614022042086069</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.918</t>
+          <t>0.61837395403857</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.023</t>
+          <t>0.489567190549182</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.124</t>
+          <t>0.471987624469414</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.134</t>
+          <t>0.421056791351303</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4.128</t>
+          <t>0.317604061340813</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.091</t>
+          <t>0.274612236835753</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>4.103</t>
+          <t>0.240250586681191</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>0.245259608994791</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>4.268</t>
+          <t>0.216213550054105</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.321</t>
+          <t>0.308629351432486</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.228</t>
+          <t>0.481177661530796</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6772.82</t>
+          <t>0.692680566612859</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6770.69</t>
+          <t>0.675899112329598</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6703.5</t>
+          <t>0.963729776865059</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6809.79</t>
+          <t>0.821791689136704</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6988.38</t>
+          <t>0.837948724849991</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7061.95</t>
+          <t>0.682489755190317</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7105.7</t>
+          <t>0.65976120085269</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7006.6</t>
+          <t>0.609371073381924</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6908.1</t>
+          <t>0.356578457783058</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6963.43</t>
+          <t>0.415758089095112</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6979.96</t>
+          <t>0.367971556656463</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>0.362782764109314</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>7319.33</t>
+          <t>0.271681569628307</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>7362.323</t>
+          <t>0.369660649708273</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>7146.911</t>
+          <t>0.580017116374236</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6234.64</t>
+          <t>8448187293.99626</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6244.23</t>
+          <t>8130389601.20029</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6174.71</t>
+          <t>7874064410.13992</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6277.92</t>
+          <t>8199648682.78154</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6444.15</t>
+          <t>8317386562.2485</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6539.08</t>
+          <t>8929258138.93522</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6609.93</t>
+          <t>8496136833.97072</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6527.4</t>
+          <t>8281259554.57812</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6446.22</t>
+          <t>8588341588.72548</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6489.13</t>
+          <t>8905853493.91647</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6490.82</t>
+          <t>9132499406.35747</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6587.61</t>
+          <t>9280962511.49692</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6822.76</t>
+          <t>9761026395.42823</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6920.38</t>
+          <t>9789994702.29348</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6705.67</t>
+          <t>8219987571.43325</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>4244679590.99994</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>4331869070.42652</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>3672016648.7754</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>4037600808.67781</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>4153526945.03676</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>4612898320.16499</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>4727620692.88732</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23.11</t>
+          <t>4861165414.26395</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>5197853079.27416</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>5397457589.95733</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>5564303725.12457</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>5633214182.87314</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>6000703567.32437</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>5716087450.23316</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>4874447963.28599</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>56.83</t>
+          <t>816191.198823022</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>57.47</t>
+          <t>717758.811742537</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>58.03</t>
+          <t>740670.899583202</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>768012.028593623</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>57.42</t>
+          <t>775795.73803652</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>840009.256681119</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>58.35</t>
+          <t>858470.512740202</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>773967.455103683</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>672630.973752934</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>599746.12093096</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>58.13</t>
+          <t>586719.49962465</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>543829.462874556</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>487170.950731641</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>56.12</t>
+          <t>451781.460145725</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>53.01</t>
+          <t>451869.086771701</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>33792.4111452511</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>33871.4874516718</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>33252.7976740022</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>33352.6973853618</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>35391.4256582544</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>36242.6852094568</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>35507.3455383301</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18.49</t>
+          <t>35935.6000301882</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>37907.1762414717</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>41855.6505260942</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>44662.4732237633</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>46616.2344096636</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>54241.3279034626</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>60100.9480487012</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>54325.2018032456</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>72793.5403970605</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>70556.6858363801</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>68113.0325542502</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>70213.9177765865</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>74082.7664092368</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16.49</t>
+          <t>80847.8731006336</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>74709.2653287235</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>74409.3552015416</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>82727.4404499184</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>94357.0334810677</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>103633.843914669</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>109948.645979436</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>130291.450020493</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>143068.466501401</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>111980.547346468</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>58.57</t>
+          <t>0.468812867103796</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>0.441463234108962</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>0.681558279987438</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.24</t>
+          <t>0.55486396438875</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>59.43</t>
+          <t>0.551488671021225</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>60.73</t>
+          <t>0.417564304726777</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>60.91</t>
+          <t>0.398151507785851</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>0.342764428639234</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>61.48</t>
+          <t>0.240169720399286</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>61.25</t>
+          <t>0.202256783281423</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>60.96</t>
+          <t>0.166510729939475</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>60.36</t>
+          <t>0.16942295928114</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>0.13699334143949</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>0.210684766503654</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>0.375677830450325</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>18.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7.1209853786912</t>
+          <t>1103.14454779461</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6.70421035800362</t>
+          <t>1134.26437391814</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7.62718343458456</t>
+          <t>974.52671145844</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7.94723073282277</t>
+          <t>1052.47264517316</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.26104914409274</t>
+          <t>1060.2223159672</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.13075211422837</t>
+          <t>1146.65995181709</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10.3114045632859</t>
+          <t>1146.47897295745</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.70685325223753</t>
+          <t>1175.8418591893</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8.06776946061647</t>
+          <t>1259.29185950047</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7.33729552481548</t>
+          <t>1319.28470618824</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7.44934438059463</t>
+          <t>1356.08883922903</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7.36702534389249</t>
+          <t>1350.76112192431</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>6.75082699066162</t>
+          <t>1406.00847426706</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6.51703522574423</t>
+          <t>1322.95402370754</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>7.60913399607839</t>
+          <t>1152.80455626055</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>6146815777.45363</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>6194614550.51682</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>5423470875.6076</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>5807390169.15527</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>6085536215.50532</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>6483305265.27474</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>6160557158.63987</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>6550687700.7201</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>7676606205.67693</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>8801874688.07441</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>8716970475.46577</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>8953575442.62403</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>9310336134.69823</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>8648241716.52702</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>6905022495.80805</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>6477569678.75465</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>6577315486.30237</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>5792492388.77335</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>6338191489.48566</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>6645050884.90531</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>6547569114.68075</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>6216987836.56812</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>6525585222.95725</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>7455583330.47133</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>8309522196.82928</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>8022787069.98824</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>8022196445.35277</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>8205005967.85566</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>7554826161.52605</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>5874038178.99445</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>-330753901.301021</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>-382700935.785542</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>-369021513.165747</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>-530801320.330387</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-559514669.399992</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>-64263849.40601</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>-56430677.9282585</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>25102477.7628513</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>221022875.205598</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>492352491.245132</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>694183405.477527</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>931378997.271262</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>1105330166.84257</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1093415555.00096</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1030984316.8136</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>1620.31290607613</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.502</t>
+          <t>1635.00039276261</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>1638.72346072187</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>1636.45178948466</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>1644.92291198699</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>1625.46421735564</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>1602.95130468523</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>1578.87862222441</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>1561.7356332978</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>1586.11898709425</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>1581.89218171183</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>1579.61106848264</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1598.62227324914</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1601.68028328743</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>1585.88767088976</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>1640.34488604704</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>1653.08120513688</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>1657.96893549664</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1656.31901542054</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>1664.81168258819</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>1642.04664356974</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1618.1681544908</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>1594.83759360852</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>1581.56093317155</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>1605.43874210356</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>1604.9943663915</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>1599.09553420011</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>1617.78175629379</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>1621.06926768452</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>1615.17180044789</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14.15</t>
+          <t>96725.5237641605</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>102366.696057867</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>31.99</t>
+          <t>101699.771226788</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>104969.377987809</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>107075.320954573</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>15.02</t>
+          <t>110832.788765628</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>100696.185240731</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>106311.677138873</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>130882.297248063</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>159190.879264687</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>170943.424743657</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>192960.40986097</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>226789.430813134</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>248132.595279107</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>16.43</t>
+          <t>181913.166040362</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>53.41</t>
+          <t>2392529947.7821</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>50.15</t>
+          <t>2291578249.33072</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>75.04</t>
+          <t>2325352013.33784</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>2432820522.77318</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>61.84</t>
+          <t>2503901006.96494</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>48.96</t>
+          <t>2780101517.74522</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>2539767714.59812</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>2441657249.3943</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>2619433021.1755</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>2864542634.64861</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>2959131825.26426</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>3127960883.12303</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>3272077603.40337</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>3344643757.09672</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>48.12</t>
+          <t>2574108826.82831</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>69.27</t>
+          <t>75831.3495973377</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>67.59</t>
+          <t>79890.6155496373</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>96.37</t>
+          <t>78082.0581520606</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>82.18</t>
+          <t>83083.1034853668</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>83.79</t>
+          <t>85453.4305373733</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>89747.980114205</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>65.98</t>
+          <t>81785.0223451439</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>60.94</t>
+          <t>85720.0656918854</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>104826.942952039</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>123953.538242074</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>136436.242345256</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>155369.566848147</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>186026.553897001</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>208723.923020259</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>152138.611332661</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6772.82</t>
+          <t>5659726814.4975</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>6770.69</t>
+          <t>5515114956.85011</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6703.5</t>
+          <t>4890894110.02602</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6809.79</t>
+          <t>5431011996.43002</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6988.38</t>
+          <t>5748895365.17485</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7061.95</t>
+          <t>6458730634.93512</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7105.7</t>
+          <t>6049937084.64636</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>7006.6</t>
+          <t>6138458692.28443</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>6908.1</t>
+          <t>6865224114.5135</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6963.43</t>
+          <t>7399298168.86228</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6979.96</t>
+          <t>7806054520.55392</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>8225557222.43054</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>7319.33</t>
+          <t>8881677901.51992</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>7362.323</t>
+          <t>8771887913.78808</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>7146.911</t>
+          <t>6799072053.35058</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6234.64</t>
+          <t>20894.1741668229</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6244.23</t>
+          <t>22476.0805082296</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6174.71</t>
+          <t>23617.7130747272</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6277.92</t>
+          <t>21886.274502442</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6444.15</t>
+          <t>21621.8904171997</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6539.08</t>
+          <t>21084.8086514232</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6609.93</t>
+          <t>18911.1628955872</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6527.4</t>
+          <t>20591.611446988</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6446.22</t>
+          <t>26055.3542960244</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6489.13</t>
+          <t>35237.341022613</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>6490.82</t>
+          <t>34507.182398401</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6587.61</t>
+          <t>37590.8430128234</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>6822.76</t>
+          <t>40762.8769161332</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>6920.38</t>
+          <t>39408.6722588476</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6705.67</t>
+          <t>29774.5547077013</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>8448.187</t>
+          <t>-3267196866.7154</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8130.39</t>
+          <t>-3223536707.51939</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7874.064</t>
+          <t>-2565542096.68817</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>8199.649</t>
+          <t>-2998191473.65685</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8317.387</t>
+          <t>-3244994358.20991</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8929.258</t>
+          <t>-3678629117.1899</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8496.137</t>
+          <t>-3510169370.04824</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8281.26</t>
+          <t>-3696801442.89013</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8588.342</t>
+          <t>-4245791093.338</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8905.853</t>
+          <t>-4534755534.21368</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>9132.499</t>
+          <t>-4846922695.28966</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>9280.963</t>
+          <t>-5097596339.30751</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>9761.026</t>
+          <t>-5609600298.11655</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>9789.995</t>
+          <t>-5427244156.69136</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8219.988</t>
+          <t>-4224963226.52227</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>114854.61053</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>122774.93584</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>112054.99439</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>112549.77093</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>113330.15737</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>108058.67783</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>99019.68258</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>110070.99521</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>138070.00793</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>158839.5881</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>160076.10059</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>172003.34448</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>199903.80459</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>208735.56022</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>167415.59572</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3921.84</t>
+          <t>0.142830901618088</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3903.08</t>
+          <t>0.134435377353781</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3844.12</t>
+          <t>0.137284544861048</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3894.96</t>
+          <t>0.137066037469961</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3973.45</t>
+          <t>0.142702623060368</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4002.83</t>
+          <t>0.132773982847976</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4037.99</t>
+          <t>0.121265104050993</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3999.39</t>
+          <t>0.123167122243585</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3935.33</t>
+          <t>0.129596563701895</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3950.53</t>
+          <t>0.136126776396385</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3935.78</t>
+          <t>0.135863032615453</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3934.96</t>
+          <t>0.145605066900012</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>4063.59</t>
+          <t>0.143005030752155</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4112.632</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3987.768</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>133127.784362746</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>150511.0878089</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>136807.643597456</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>137032.009325101</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>136351.930258648</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>135897.23871761</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>128638.440508168</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>140953.50530439</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>174679.259001201</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>198006.744264434</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>201662.713361205</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>211588.521117675</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>248571.027188134</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>262905.781776772</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>222136.709758279</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4244.68</t>
+          <t>143141.090244378</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4331.869</t>
+          <t>161542.668371692</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3672.017</t>
+          <t>147085.249329839</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4037.601</t>
+          <t>147365.163379276</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4153.527</t>
+          <t>146513.806072053</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4612.898</t>
+          <t>145381.994219881</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4727.621</t>
+          <t>136976.405454252</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4861.165</t>
+          <t>149877.465676238</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5197.853</t>
+          <t>185578.561508121</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>5397.458</t>
+          <t>210743.792381888</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>5564.304</t>
+          <t>215298.41297581</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>5633.214</t>
+          <t>225476.100933943</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>6000.704</t>
+          <t>264880.656011057</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>5716.087</t>
+          <t>280324.241073704</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>4874.448</t>
+          <t>237231.086161039</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>545298.549566519</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>595671.882688816</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>68.16</t>
+          <t>546296.317448332</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>55.49</t>
+          <t>550559.584078313</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>55.15</t>
+          <t>559827.924355327</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>546059.288310521</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>39.82</t>
+          <t>516590.591712231</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>572674.271663728</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>700425.904121031</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>789646.203294406</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>808590.697184944</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>16.94</t>
+          <t>855373.532513009</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>985730.606451543</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>37.57</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>143141.090244378</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>149845.764626259</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>153009.12433474</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>158833.376482047</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>162872.121386245</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>178176.232055176</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>190976.721517479</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>196148.574637276</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>198444.141333506</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>204866.178068768</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.587</t>
+          <t>215662.279492884</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>220237.056421005</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>233223.897723086</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>236013.372408089</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>228839.713418951</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>133127.784362746</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>139368.926890817</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>142042.186841521</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>147728.752951229</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>151644.686131021</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>166730.278943514</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>179849.433456003</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>185100.922674331</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>187522.568122355</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>193222.90210259</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>201851.287700017</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>207426.50935102</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>220500.176045215</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>223347.6713283</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>215879.258804695</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>77885.4834856216</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>80079.3743283085</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>74998.0413001609</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>75463.020580724</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>79888.9132679466</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>72502.466580119</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>62644.4118557478</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>70534.6420237624</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>90772.7903018787</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>107491.992148112</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>109857.58426419</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>124546.720426057</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>140964.435688943</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>150830.402136296</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>116473.816238961</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>6234639999.99358</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>6244229999.9936</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>6174710000</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>6277920000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>6444150000.00593</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6539080000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6609930000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>6527400000.00494</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>6446220000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6489130000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6490820000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>6587610000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>6822760000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6920380000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>6705669998.77628</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>6772819999.99282</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6770689999.99285</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6703500000</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6809790000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>6988380000.0107</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>7061950000.00911</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>7105700000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>7006600000.00862</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>6908100000</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6963430000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6979960000</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>7.072e+09</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>7319330000</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>7362323182.22011</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>7146911162.50548</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3921840000</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3903080000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3844120000</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3894960000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3973450000</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>4002830000</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4037990000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3999390000</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3935330000</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>3950530000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3935780000</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3934960000</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4063590000</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4112632066.22711</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3987768359.95138</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4128899.99999584</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4095799.9999959</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4043200</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4111400</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4197700.00000615</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4300700.00000532</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4391200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4393300.00000522</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4367900</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4337400</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4348900</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4422500</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4524300</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4541646.26335567</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4424861.28133468</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3847799.99999621</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3819099.99999627</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3768000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3836300</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3917600.00000346</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4022900</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4123600</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4134200.00000303</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4127600</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4091200</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4103200</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4170400</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4267900</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4320700</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4228338.56512301</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6772819999.99282</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6770689999.99285</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>6703500000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6809790000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6988380000.0107</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>7061950000.00911</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7105700000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>7006600000.00862</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6908100000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6963430000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6979960000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>7.072e+09</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>7319330000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>7362323182.22011</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7146911162.50548</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6234639999.99358</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6244229999.9936</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>6174710000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6277920000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>6444150000.00593</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6539080000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6609930000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>6527400000.00494</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>6446220000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6489130000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>6490820000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6587610000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6822760000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6920380000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6705669998.77628</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.175632394391622</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.178519764421943</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.182521612994752</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.185480918571493</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.199769360570896</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.218077092896323</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.225195429041695</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.231065372362702</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.22077703781729</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.238035604533249</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.249053314488781</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.25943802992654</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.262575913097484</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.27981093651643</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.292918479894697</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.568263560293997</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.574674634470877</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.580260119671008</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.586000513061219</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.574163857675759</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.582930939050782</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.583532617697635</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.584072145887833</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.583415741425941</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.585317212081492</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.581267224553589</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.574570886085595</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.570379798923343</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.561167767493832</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.530134638009854</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.256104045314381</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.24680560110718</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.23721826733424</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.228518568367287</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.226066781753345</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.198991968052896</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.19127195326067</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.184862481749466</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.195807220756769</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.176647183385259</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.16967946095763</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.165991083987865</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.167044287979174</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.159021295989738</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.176946882095448</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.127366819728121</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.129160847897513</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.133416182165984</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.137055627698075</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.1464484811306</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.164891415642487</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.172730142899479</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.176779161263421</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.179782694531231</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.187163260028709</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.198873353722608</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.210336155623757</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.215609489132964</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.230321399524585</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.240881984702742</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.585702966243725</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.591529283873456</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.597372678209279</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.602366870709266</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.594291764382177</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.607277147009464</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.609096810665625</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.610223712014477</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.614762393708153</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.612470415297403</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.609644581664782</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.603618796500982</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.603726782905289</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.598529920241151</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.566309634240847</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.286930214028155</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.279309868229031</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.269211139624737</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.26057750159266</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.259259754487222</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.227831437348049</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.218173046434896</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.212997126722102</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.205454911760616</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.200366324673888</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.19148206461261</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.186045047875261</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.180663727961747</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.171148680234264</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.192808381056411</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>461976.65331</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>501511.41338</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>466168.81334</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>468861.31007</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>476120.03486</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>466126.22559</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>430428.36138</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>466075.03516</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>573860.72027</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>666076.61884</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>694302.57719</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>753739.90604</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>880097.95041</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>949568.28984</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>757060.99647</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>221026.57373</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>241622.0427</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>222083.29063</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>222828.18396</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>226402.71934</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>217884.4608</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>199620.81731</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>220412.1077</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>276351.35181</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>318235.78453</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>325155.99724</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>350022.82136</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>405845.0917</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>431154.64321</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>353704.9024</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3883063.05764445</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4018765.57132922</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>4144897.71115209</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4291173.96676717</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4451909.0550342</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4621620.99180891</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4765026.77031318</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4883940.32262649</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>5000945.27065932</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5138989.3150617</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>5306922.67425119</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>5502674.76391365</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>5725293.18762794</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
